--- a/data/excel/prosandcons.xlsx
+++ b/data/excel/prosandcons.xlsx
@@ -1,17 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pros &amp; Cons" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pros &amp; Cons'!$A$2:$D$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,47 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -75,44 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -478,369 +413,2235 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bluestock Fintech — Nifty 100  |  Pros &amp; Cons  |  16 records</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Bluestock Fintech — Nifty 100  |  Prosandcons  |  111 records</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>pros</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>cons</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Company is expected to give good quarter</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Stock is trading at 2.76 times its book value</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Company has delivered good profit growth of 23.4% CAGR over last 5 years</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Company has low interest coverage ratio.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Company has been maintaining a healthy dividend payout of 22.9%</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Contingent liabilities of Rs.24,09,821 Cr.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Company's median sales growth is 16.4% of last 10 years</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Earnings include an other income of Rs.1,55,870 Cr.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Company is almost debt free.</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Stock is trading at 9.11 times its book value</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Company is expected to give good quarter</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Tax rate seems low</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Company has a low return on equity of 12.9% over last 3 years.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Earnings include an other income of Rs.1,657 Cr.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>SBILIFE</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Dividend payout has been low at 14.0% of profits over last 3 years</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Company has a good return on equity (ROE) track record: 3 Years ROE 30.9%</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Stock is trading at 9.03 times its book value</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>INFY</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Company has been maintaining a healthy dividend payout of 63.3%</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Promoter holding is low: 14.4%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>The company has delivered a poor sales growth of 8.75% over past five years.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>WIPRO</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Dividend payout has been low at 12.2% of profits over last 3 years</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Company is almost debt free.</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Stock is trading at 15.2 times its book value</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Company has a good return on equity (ROE) track record: 3 Years ROE 47.4%</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>The company has delivered a poor sales growth of 10.5% over past five years.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Company has been maintaining a healthy dividend payout of 66.2%</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>NULL</t>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TATACAP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ENRIN</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>TMCV</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Company has a good track record of return on equity (ROE): 3 Years ROE 20%. Company is virtually debt free.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>The stock is trading at a high valuation multiple relative to book value.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>